--- a/input/input_PR_BIP.xlsx
+++ b/input/input_PR_BIP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pennstateoffice365-my.sharepoint.com/personal/izg5132_psu_edu/Documents/06_PHD_EME_PSU/00 RESEARCH/PHD UHS PROJECT/02_UHS EXPERIMENTS/H2 DISPLACEMENT EXPERIMENT/Input/For_github_repo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pennstateoffice365-my.sharepoint.com/personal/izg5132_psu_edu/Documents/06_PHD_EME_PSU/00 RESEARCH/PHD UHS PROJECT/MATLAB-GITHUB/UHS-CF-Dispersion-Exps2/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="225" documentId="11_F25DC773A252ABDACC10485949585E945ADE58F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{773E6094-5E79-45B5-A6AD-3F0423097211}"/>
+  <xr:revisionPtr revIDLastSave="230" documentId="11_F25DC773A252ABDACC10485949585E945ADE58F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3CAE750-8C4A-4BCA-B66B-5AC54002934F}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
   <si>
     <t>H2</t>
   </si>
@@ -69,6 +69,12 @@
   </si>
   <si>
     <t>MPa</t>
+  </si>
+  <si>
+    <t>Xe</t>
+  </si>
+  <si>
+    <t>assumed</t>
   </si>
 </sst>
 </file>
@@ -386,13 +392,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="4" width="10.85546875" customWidth="1"/>
+    <col min="1" max="4" width="10.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -406,7 +412,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C2" t="s">
         <v>10</v>
       </c>
@@ -414,7 +420,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -428,7 +434,7 @@
         <v>268.3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -442,7 +448,7 @@
         <v>92.99</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -456,7 +462,7 @@
         <v>70.099999999999994</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -470,35 +476,58 @@
         <v>559.29999999999995</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>137.30000000000001</v>
+        <v>265.89999999999998</v>
       </c>
       <c r="D7">
-        <v>194.2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>268.3</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
       <c r="B8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>137.30000000000001</v>
+      </c>
+      <c r="D8">
+        <v>194.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
         <v>2</v>
       </c>
-      <c r="C8">
+      <c r="C9">
         <v>37.9</v>
       </c>
-      <c r="D8">
+      <c r="D9">
         <v>37.200000000000003</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{7cf48d45-3ddb-4389-a9c1-c115526eb52e}" enabled="0" method="" siteId="{7cf48d45-3ddb-4389-a9c1-c115526eb52e}" removed="1"/>
+</clbl:labelList>
 </file>